--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486782_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486782_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. SOTO RODRIGUEZ</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9359</v>
+        <v>4.433</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0623</v>
+        <v>4.9243</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1264</v>
+        <v>-0.4913</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1171</v>
+        <v>2.4581</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4419</v>
+        <v>-1.0686</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3247</v>
+        <v>3.5267</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1046</v>
+        <v>4.1289</v>
       </c>
       <c r="K2" t="n">
-        <v>5.0977</v>
+        <v>-0.0332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0069</v>
+        <v>4.162</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9874</v>
+        <v>-1.6707</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6558</v>
+        <v>-1.0354</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3316</v>
+        <v>-0.6354</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2741</v>
+        <v>-0.4619</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9577</v>
+        <v>-0.104</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6836</v>
+        <v>-0.3579</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>I. SOTO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2843</v>
+        <v>3.8341</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6763</v>
+        <v>6.035</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.392</v>
+        <v>-2.2009</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4581</v>
+        <v>2.1171</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0686</v>
+        <v>3.4419</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5267</v>
+        <v>-1.3247</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1289</v>
+        <v>5.1046</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0332</v>
+        <v>5.0977</v>
       </c>
       <c r="L3" t="n">
-        <v>4.162</v>
+        <v>0.0069</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6707</v>
+        <v>-2.9874</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0354</v>
+        <v>-1.6558</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6354</v>
+        <v>-1.3316</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6106</v>
+        <v>0.1723</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.352</v>
+        <v>0.9304</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2586</v>
+        <v>-0.7581</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6991000000000001</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0321</v>
+        <v>2.4378</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2176</v>
+        <v>2.5488</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1855</v>
+        <v>-0.111</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6572</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1527</v>
+        <v>0.5584</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5993</v>
+        <v>0.9306</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4466</v>
+        <v>-0.3721</v>
       </c>
       <c r="V4" t="n">
         <v>1.1851</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6177</v>
+        <v>1.0535</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9666</v>
+        <v>-0.7045</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5842</v>
+        <v>1.7581</v>
       </c>
       <c r="G5" t="n">
         <v>1.3747</v>
@@ -844,13 +844,13 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6564</v>
+        <v>-0.2206</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4139</v>
+        <v>-0.1519</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2425</v>
+        <v>-0.0687</v>
       </c>
       <c r="V5" t="n">
         <v>0.2856</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3902</v>
+        <v>-0.4578</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5524</v>
+        <v>0.5593</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9426</v>
+        <v>-1.0171</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3957</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0055</v>
+        <v>-0.062</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4686</v>
+        <v>0.4756</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4631</v>
+        <v>-0.5376</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7623</v>
+        <v>-1.7568</v>
       </c>
       <c r="E7" t="n">
-        <v>0.336</v>
+        <v>0.3912</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0983</v>
+        <v>-2.148</v>
       </c>
       <c r="G7" t="n">
         <v>0.1631</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2537</v>
+        <v>-0.2482</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0828</v>
+        <v>-0.0277</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1709</v>
+        <v>-0.2206</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8995</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6749</v>
+        <v>-2.93</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0222</v>
+        <v>-0.2329</v>
       </c>
       <c r="F8" t="n">
         <v>-2.6971</v>
@@ -1078,10 +1078,10 @@
         <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1655</v>
+        <v>-0.4206</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2756</v>
+        <v>0.0205</v>
       </c>
       <c r="U8" t="n">
         <v>-0.4411</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3294</v>
+        <v>-4.9515</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3477</v>
+        <v>-4.2925</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9818</v>
+        <v>-0.659</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0783</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4675</v>
+        <v>-1.0895</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4693</v>
+        <v>-0.4142</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9982</v>
+        <v>-0.6754</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6653</v>
+        <v>-5.5275</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0889</v>
+        <v>-2.8269</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5765</v>
+        <v>-2.7006</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0417</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3034</v>
+        <v>-0.1655</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5797</v>
+        <v>-0.3177</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2763</v>
+        <v>0.1522</v>
       </c>
       <c r="V10" t="n">
         <v>-2.741</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1222</v>
+        <v>-5.8064</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0262</v>
+        <v>-5.6607</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.096</v>
+        <v>-0.1457</v>
       </c>
       <c r="G11" t="n">
         <v>-0.669</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1363</v>
+        <v>-0.8205</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8554</v>
+        <v>-0.4899</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2809</v>
+        <v>-0.3306</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.6867</v>
+        <v>-7.262</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7299</v>
+        <v>-4.2058</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9568</v>
+        <v>-3.0562</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0716</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2868</v>
+        <v>0.1379</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0004</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2865</v>
+        <v>-0.3858</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9421</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.761</v>
+        <v>-16.9336</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.292500000000002</v>
+        <v>-3.464700000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-13.4688</v>
@@ -1468,10 +1468,10 @@
         <v>11.5846</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.4479</v>
+        <v>-2.6202</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5477000000000002</v>
+        <v>1.3754</v>
       </c>
       <c r="U13" t="n">
         <v>-3.9957</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.5454</v>
+        <v>7.9765</v>
       </c>
       <c r="E14" t="n">
-        <v>10.2932</v>
+        <v>6.9837</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2523</v>
+        <v>0.9928</v>
       </c>
       <c r="G14" t="n">
         <v>3.2184</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>6.134</v>
+        <v>2.5651</v>
       </c>
       <c r="T14" t="n">
-        <v>5.3223</v>
+        <v>2.0128</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8117</v>
+        <v>0.5523</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8388</v>
+        <v>5.9103</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1768</v>
+        <v>4.4757</v>
       </c>
       <c r="F15" t="n">
-        <v>2.662</v>
+        <v>1.4345</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7808</v>
+        <v>3.4507</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9797</v>
+        <v>1.9587</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1989</v>
+        <v>1.4921</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5271</v>
+        <v>4.7142</v>
       </c>
       <c r="K15" t="n">
-        <v>0.946</v>
+        <v>2.3043</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5810999999999999</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2537</v>
+        <v>-1.2635</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0337</v>
+        <v>-0.3456</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.78</v>
+        <v>-0.9179</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5447</v>
+        <v>1.0275</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4959</v>
+        <v>0.5305</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0488</v>
+        <v>0.4969</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5133</v>
+        <v>2.7836</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0845</v>
+        <v>2.1271</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5712</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3478</v>
+        <v>5.0593</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3381</v>
+        <v>2.3836</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0097</v>
+        <v>2.6757</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4507</v>
+        <v>1.7808</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9587</v>
+        <v>1.9797</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4921</v>
+        <v>-0.1989</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7142</v>
+        <v>1.5271</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3043</v>
+        <v>0.946</v>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2635</v>
+        <v>0.2537</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3456</v>
+        <v>1.0337</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9179</v>
+        <v>-0.78</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.535</v>
+        <v>1.7653</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6071</v>
+        <v>0.7028</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0722</v>
+        <v>1.0625</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7836</v>
+        <v>1.5133</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1271</v>
+        <v>2.0845</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6565</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9394</v>
+        <v>1.1651</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1445</v>
+        <v>2.438</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2051</v>
+        <v>-1.2729</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5528</v>
+        <v>1.5093</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2136</v>
+        <v>0.5372</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7664</v>
+        <v>0.972</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1725</v>
+        <v>2.5039</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6969</v>
+        <v>1.1588</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5244</v>
+        <v>1.3451</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.9946</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4833</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.242</v>
+        <v>-0.3731</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7723</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R17" t="n">
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3917</v>
+        <v>-0.0619</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7443</v>
+        <v>0.0893</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3526</v>
+        <v>-0.1512</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3282</v>
+        <v>1.8415</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>2.741</v>
       </c>
       <c r="X17" t="n">
         <v>-0.8995</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4881</v>
+        <v>1.0028</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7141</v>
+        <v>2.1445</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2259</v>
+        <v>-1.1417</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5093</v>
+        <v>-0.5528</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5372</v>
+        <v>0.2136</v>
       </c>
       <c r="I18" t="n">
-        <v>0.972</v>
+        <v>-0.7664</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5039</v>
+        <v>0.1725</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1588</v>
+        <v>0.6969</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3451</v>
+        <v>-0.5244</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9946</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.4833</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3731</v>
+        <v>-0.242</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7388</v>
+        <v>0.4551</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6347</v>
+        <v>0.7443</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1041</v>
+        <v>-0.2892</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8415</v>
+        <v>0.3282</v>
       </c>
       <c r="W18" t="n">
-        <v>2.741</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
         <v>-0.8995</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. RODRÍGUEZ GONZÁLEZ</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.015</v>
+        <v>0.8099</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1697</v>
+        <v>-0.0306</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1547</v>
+        <v>0.8404</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1295</v>
+        <v>1.6305</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3654</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7641</v>
+        <v>2.5342</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3228</v>
+        <v>1.0525</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0207</v>
+        <v>-0.903</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3022</v>
+        <v>1.9555</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1934</v>
+        <v>0.578</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3447</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5381</v>
+        <v>0.5786</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3144</v>
+        <v>-0.8206</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4688</v>
+        <v>-0.1177</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1544</v>
+        <v>-0.703</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>M. LOZANO MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4934</v>
+        <v>0.105</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9614</v>
+        <v>1.2367</v>
       </c>
       <c r="F20" t="n">
-        <v>0.468</v>
+        <v>-1.1317</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6305</v>
+        <v>0.76</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-1.0281</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5342</v>
+        <v>1.7882</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0525</v>
+        <v>1.3679</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.903</v>
+        <v>0.1448</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9555</v>
+        <v>1.2231</v>
       </c>
       <c r="M20" t="n">
-        <v>0.578</v>
+        <v>-0.6079</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.173</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5786</v>
+        <v>0.5651</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1239</v>
+        <v>-0.8481</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0485</v>
+        <v>-0.1312</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0755</v>
+        <v>-0.7169</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. LOZANO MARTINEZ</t>
+          <t>I. RODRÍGUEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5417999999999999</v>
+        <v>0.0454</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9264</v>
+        <v>-0.0371</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4682</v>
+        <v>0.0825</v>
       </c>
       <c r="G21" t="n">
-        <v>0.76</v>
+        <v>1.1295</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0281</v>
+        <v>0.3654</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7882</v>
+        <v>0.7641</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3679</v>
+        <v>1.3228</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1448</v>
+        <v>0.0207</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2231</v>
+        <v>1.3022</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6079</v>
+        <v>-0.1934</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.173</v>
+        <v>0.3447</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5651</v>
+        <v>-0.5381</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
         <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4949</v>
+        <v>0.3447</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4415</v>
+        <v>0.2619</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0534</v>
+        <v>0.0828</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.3408</v>
       </c>
       <c r="E22" t="n">
         <v>-2.257</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5549</v>
+        <v>1.9163</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7266</v>
@@ -2170,13 +2170,13 @@
         <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4798</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>0.4135</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0664</v>
+        <v>0.4278</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.676</v>
+        <v>-2.5933</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0755</v>
+        <v>-3.8687</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3995</v>
+        <v>1.2754</v>
       </c>
       <c r="G23" t="n">
         <v>-1.959</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.524</v>
+        <v>-0.4413</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7174</v>
+        <v>-0.5105</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1934</v>
+        <v>0.0692</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>17.7612</v>
+        <v>19.1402</v>
       </c>
       <c r="E24" t="n">
-        <v>13.4689</v>
+        <v>13.46879999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>4.2925</v>
+        <v>5.6713</v>
       </c>
       <c r="G24" t="n">
-        <v>8.240800000000002</v>
+        <v>8.2408</v>
       </c>
       <c r="H24" t="n">
         <v>5.5168</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7241</v>
+        <v>2.724099999999999</v>
       </c>
       <c r="J24" t="n">
         <v>11.735</v>
@@ -2317,7 +2317,7 @@
         <v>-1.7641</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9654</v>
+        <v>-0.9653999999999996</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.5848</v>
@@ -2326,19 +2326,19 @@
         <v>10.6193</v>
       </c>
       <c r="S24" t="n">
-        <v>3.448</v>
+        <v>4.827</v>
       </c>
       <c r="T24" t="n">
-        <v>3.9956</v>
+        <v>3.9957</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5474999999999999</v>
+        <v>0.8311999999999998</v>
       </c>
       <c r="V24" t="n">
         <v>7.037800000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>9.322700000000001</v>
+        <v>9.322699999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-2.2849</v>
